--- a/equipment_maintenance_forms/018_voc_waste_gas_maintenance_checklist--equipment_maintenance_forms.xlsx
+++ b/equipment_maintenance_forms/018_voc_waste_gas_maintenance_checklist--equipment_maintenance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>First Page</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gas_system_inspection</t>
+          <t>Inspect Gas System Components</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>second_page</t>
+          <t>Maintenance Activities</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>maintenance_activities</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>maintenance_activities</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Page 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>facility_email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Facility Email</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>submit_button</t>
+          <t>facility_phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Facility Phone</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>submit_button</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>facility_email</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>facility_phone</t>
+          <t>facility_email_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>facility_phone</t>
+          <t>Facility Email 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>submit_button</t>
+          <t>facility_phone_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Facility Phone 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>submit_button_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>facility_email</t>
+          <t>Submit Button 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>facility_phone</t>
+          <t>gas_inlet</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>facility_phone</t>
+          <t>Gas Inlet</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>submit_button</t>
+          <t>gas_outlet</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Gas Outlet</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,80 +824,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>page_4</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>gas_inlet</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>gas_inlet_label</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>gas_outlet</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>gas_outlet_label</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>page_5</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>page_5</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -917,9 +848,9 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{1:_'valve_1'}</t>
+          <t>valve_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{1: 'Valve 1'}</t>
+          <t>Valve 1</t>
         </is>
       </c>
     </row>
@@ -964,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{2:_'valve_2'}</t>
+          <t>valve_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{2: 'Valve 2'}</t>
+          <t>Valve 2</t>
         </is>
       </c>
     </row>
@@ -981,63 +912,63 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{3:_'valve_3'}</t>
+          <t>valve_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{3: 'Valve 3'}</t>
+          <t>Valve 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>maintenance_activities_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{1:_'maintenance_activity_1'}</t>
+          <t>maintenance_activity_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{1: 'Maintenance Activity 1'}</t>
+          <t>Maintenance Activity 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>maintenance_activities_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{2:_'maintenance_activity_2'}</t>
+          <t>maintenance_activity_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{2: 'Maintenance Activity 2'}</t>
+          <t>Maintenance Activity 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>maintenance_activities_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{3:_'maintenance_activity_3'}</t>
+          <t>maintenance_activity_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{3: 'Maintenance Activity 3'}</t>
+          <t>Maintenance Activity 3</t>
         </is>
       </c>
     </row>
